--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-gesichtsfeld-einheiten-ucum.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-gesichtsfeld-einheiten-ucum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:24:58+00:00</t>
+    <t>2026-09-14T13:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-gesichtsfeld-einheiten-ucum.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-gesichtsfeld-einheiten-ucum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:41:44+00:00</t>
+    <t>2026-09-14T14:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
